--- a/backend/data/ci_s3_partial_some_unmatched.xlsx
+++ b/backend/data/ci_s3_partial_some_unmatched.xlsx
@@ -1,41 +1,129 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lam.le_tentree\Downloads\25026-p2-QuanLyHangDenKho-TuongLam-main\backend\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83FF8C96-42D6-456A-B1A8-62267D3DBE43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Commercial Invoice" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="27">
+  <si>
+    <t>COMMERCIAL INVOICE</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Invoice No:</t>
+  </si>
+  <si>
+    <t>CI-S3-PARTIAL-UNM-001</t>
+  </si>
+  <si>
+    <t>Invoice Date:</t>
+  </si>
+  <si>
+    <t>2026-04-15</t>
+  </si>
+  <si>
+    <t>PO Shipping Summary</t>
+  </si>
+  <si>
+    <t>SKU Code</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>Unit Price (USD)</t>
+  </si>
+  <si>
+    <t>Total Price (USD)</t>
+  </si>
+  <si>
+    <t>Weight (kg)</t>
+  </si>
+  <si>
+    <t>CBM</t>
+  </si>
+  <si>
+    <t>TEN7101-FGN-XS</t>
+  </si>
+  <si>
+    <t>FW26 Fleece Jacket - Forest Green XS</t>
+  </si>
+  <si>
+    <t>TEN7101-FGN-S</t>
+  </si>
+  <si>
+    <t>FW26 Fleece Jacket - Forest Green S</t>
+  </si>
+  <si>
+    <t>TEN7101-FGN-UNKNOWN</t>
+  </si>
+  <si>
+    <t>FW26 Fleece Jacket - Forest Green UNKNOWN</t>
+  </si>
+  <si>
+    <t>PO-FW26-003</t>
+  </si>
+  <si>
+    <t>TEN7301-IDG-XS</t>
+  </si>
+  <si>
+    <t>Hemp Denim Straight Pant Indigo</t>
+  </si>
+  <si>
+    <t>TEN7301-IDG-S</t>
+  </si>
+  <si>
+    <t>TEN7301-IDG-M</t>
+  </si>
+  <si>
+    <t>TEN7301-IDG-L</t>
+  </si>
+  <si>
+    <t>TEN7301-IDG-XL</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -64,14 +152,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,245 +494,253 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>COMMERCIAL INVOICE</v>
-      </c>
-      <c r="B1" t="str">
-        <v/>
-      </c>
-      <c r="C1" t="str">
-        <v/>
-      </c>
-      <c r="D1" t="str">
-        <v/>
-      </c>
-      <c r="E1" t="str">
-        <v/>
-      </c>
-      <c r="F1" t="str">
-        <v/>
-      </c>
-      <c r="G1" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Invoice No:</v>
-      </c>
-      <c r="B2" t="str">
-        <v>CI-S3-PARTIAL-UNM-001</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Invoice Date:</v>
-      </c>
-      <c r="D2" t="str">
-        <v>2026-04-15</v>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>PO Shipping Summary</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>PO-FW26-001</v>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>20</v>
       </c>
       <c r="B4">
-        <v>3800</v>
+        <f>SUM(C11:C18)</f>
+        <v>8000</v>
       </c>
       <c r="C4">
         <v>190</v>
       </c>
       <c r="D4">
-        <v>760</v>
+        <f>SUM(F11:F18)</f>
+        <v>1520</v>
       </c>
       <c r="E4">
-        <v>9.5</v>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v/>
-      </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v/>
-      </c>
-      <c r="B6" t="str">
-        <v/>
-      </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v/>
-      </c>
-      <c r="B7" t="str">
-        <v/>
-      </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v/>
-      </c>
-      <c r="B8" t="str">
-        <v/>
-      </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v/>
-      </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>SKU Code</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Description</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Qty</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Unit Price (USD)</v>
-      </c>
-      <c r="E10" t="str">
-        <v>Total Price (USD)</v>
-      </c>
-      <c r="F10" t="str">
-        <v>Weight (kg)</v>
-      </c>
-      <c r="G10" t="str">
-        <v>CBM</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>TEN7101-FGN-XS</v>
-      </c>
-      <c r="B11" t="str">
-        <v>FW26 Fleece Jacket - Forest Green XS</v>
+        <f>SUM(G11:G18)</f>
+        <v>24.5</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
       </c>
       <c r="C11">
         <v>800</v>
@@ -643,6 +749,7 @@
         <v>16.5</v>
       </c>
       <c r="E11">
+        <f>C11*D11</f>
         <v>13200</v>
       </c>
       <c r="F11">
@@ -652,12 +759,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>TEN7101-FGN-S</v>
-      </c>
-      <c r="B12" t="str">
-        <v>FW26 Fleece Jacket - Forest Green S</v>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
       </c>
       <c r="C12">
         <v>1400</v>
@@ -666,6 +773,7 @@
         <v>16.5</v>
       </c>
       <c r="E12">
+        <f t="shared" ref="E12:E18" si="0">C12*D12</f>
         <v>23100</v>
       </c>
       <c r="F12">
@@ -675,12 +783,12 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>TEN7101-FGN-UNKNOWN</v>
-      </c>
-      <c r="B13" t="str">
-        <v>FW26 Fleece Jacket - Forest Green UNKNOWN</v>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
       </c>
       <c r="C13">
         <v>1600</v>
@@ -689,6 +797,7 @@
         <v>16.5</v>
       </c>
       <c r="E13">
+        <f t="shared" si="0"/>
         <v>26400</v>
       </c>
       <c r="F13">
@@ -698,55 +807,130 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v/>
-      </c>
-      <c r="B14" t="str">
-        <v/>
-      </c>
-      <c r="C14" t="str">
-        <v/>
-      </c>
-      <c r="D14" t="str">
-        <v/>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v/>
-      </c>
-      <c r="B15" t="str">
-        <v/>
-      </c>
-      <c r="C15" t="str">
-        <v/>
-      </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14">
+        <v>400</v>
+      </c>
+      <c r="D14" s="1">
+        <v>19.8</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>7920</v>
+      </c>
+      <c r="F14">
+        <v>80</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15">
+        <v>800</v>
+      </c>
+      <c r="D15" s="1">
+        <v>19.8</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>15840</v>
+      </c>
+      <c r="F15">
+        <v>160</v>
+      </c>
+      <c r="G15">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D16" s="1">
+        <v>19.8</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>23760</v>
+      </c>
+      <c r="F16">
+        <v>200</v>
+      </c>
+      <c r="G16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D17" s="1">
+        <v>19.8</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="0"/>
+        <v>23760</v>
+      </c>
+      <c r="F17">
+        <v>200</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18">
+        <v>600</v>
+      </c>
+      <c r="D18" s="1">
+        <v>19.8</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="0"/>
+        <v>11880</v>
+      </c>
+      <c r="F18">
+        <v>120</v>
+      </c>
+      <c r="G18">
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G15"/>
+    <ignoredError sqref="A1:G3 A5:G10 C4 A12:D13 A11:D11 F11:G11 F12:G13 F4:G4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>